--- a/data/trans_orig/P37-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P37-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han vacunado de la gripe en la última campaña en 2007</t>
+          <t>Población según si se han vacunado de la gripe en la última campaña en 2007 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10226</t>
+          <t>10219</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28141</t>
+          <t>28454</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5588</t>
+          <t>5569</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20263</t>
+          <t>19443</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20227</t>
+          <t>19771</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41480</t>
+          <t>43360</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>465073</t>
+          <t>464760</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>482988</t>
+          <t>482995</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>446310</t>
+          <t>447130</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>460985</t>
+          <t>461004</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>918307</t>
+          <t>916427</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>939560</t>
+          <t>940016</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23047</t>
+          <t>23271</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46865</t>
+          <t>46433</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,82 +1091,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,31%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>23471</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>15164</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>35548</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3,75%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>5,68%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>56755</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>42534</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>71901</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>4,17%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>3,13%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,37%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>23471</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>15107</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>35477</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,75%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>5,67%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>56755</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>43619</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>74508</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>688624</t>
+          <t>689056</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>712442</t>
+          <t>712218</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,82 +1204,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>96,84%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>602023</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>589946</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>610330</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>96,25%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>94,32%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>97,58%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1241</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1304227</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>1289081</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>1318448</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>95,83%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>94,72%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>96,87%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>602023</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>590017</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>610387</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,25%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>94,33%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>97,58%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1241</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1304227</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1286474</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1317363</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>95,83%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>94,53%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>96,79%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25002</t>
+          <t>23797</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48198</t>
+          <t>48904</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31147</t>
+          <t>31904</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58609</t>
+          <t>58314</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62940</t>
+          <t>61555</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>98539</t>
+          <t>96705</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>590470</t>
+          <t>589764</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>613666</t>
+          <t>614871</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>630154</t>
+          <t>630449</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>657616</t>
+          <t>656859</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1228892</t>
+          <t>1230726</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1264491</t>
+          <t>1265876</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,36%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28330</t>
+          <t>27069</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53658</t>
+          <t>52360</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18302</t>
+          <t>16930</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37432</t>
+          <t>36617</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50459</t>
+          <t>49451</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>83964</t>
+          <t>82394</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>465489</t>
+          <t>466787</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>490817</t>
+          <t>492078</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>478210</t>
+          <t>479025</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>497340</t>
+          <t>498712</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>950825</t>
+          <t>952395</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>984330</t>
+          <t>985338</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,22%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56902</t>
+          <t>57791</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87539</t>
+          <t>86268</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>56231</t>
+          <t>57085</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>87182</t>
+          <t>88087</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>123010</t>
+          <t>122776</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>167589</t>
+          <t>163212</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,64%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>299171</t>
+          <t>300442</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>329808</t>
+          <t>328919</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>316804</t>
+          <t>315899</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>347755</t>
+          <t>346901</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>623107</t>
+          <t>627484</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>667686</t>
+          <t>667920</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,47%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>100880</t>
+          <t>98930</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>133083</t>
+          <t>132815</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>134488</t>
+          <t>133731</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>169823</t>
+          <t>168815</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>243786</t>
+          <t>244513</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>290486</t>
+          <t>291984</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>46,01%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>158586</t>
+          <t>158854</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>190789</t>
+          <t>192739</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>173111</t>
+          <t>174119</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>208446</t>
+          <t>209203</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>344117</t>
+          <t>342619</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>390817</t>
+          <t>390090</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,47%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>130218</t>
+          <t>129604</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>155031</t>
+          <t>155416</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>187540</t>
+          <t>186620</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>225493</t>
+          <t>223557</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>326264</t>
+          <t>325851</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>371624</t>
+          <t>370871</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>68,2%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>54852</t>
+          <t>54467</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>79665</t>
+          <t>80279</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>108415</t>
+          <t>110351</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>146368</t>
+          <t>147288</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>172167</t>
+          <t>172920</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>217527</t>
+          <t>217940</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,08%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>415220</t>
+          <t>417913</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>490166</t>
+          <t>490096</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>491392</t>
+          <t>494083</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>576847</t>
+          <t>574991</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>936157</t>
+          <t>933527</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1051755</t>
+          <t>1045896</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2784613</t>
+          <t>2784683</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2859559</t>
+          <t>2856866</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2800453</t>
+          <t>2802309</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2885908</t>
+          <t>2883217</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5600324</t>
+          <t>5606183</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5715922</t>
+          <t>5718552</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,97%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han vacunado de la gripe en la última campaña en 2012</t>
+          <t>Población según si se han vacunado de la gripe en la última campaña en 2012 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18081</t>
+          <t>17760</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39015</t>
+          <t>39674</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7853</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23754</t>
+          <t>23272</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29785</t>
+          <t>31001</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56372</t>
+          <t>57740</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>413179</t>
+          <t>412520</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>434113</t>
+          <t>434434</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>406476</t>
+          <t>406958</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>422377</t>
+          <t>422330</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>826052</t>
+          <t>824684</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>852639</t>
+          <t>851423</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,49%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29170</t>
+          <t>30150</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56236</t>
+          <t>56153</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22207</t>
+          <t>22817</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45938</t>
+          <t>45283</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57572</t>
+          <t>57810</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91566</t>
+          <t>92661</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>630851</t>
+          <t>630934</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>657917</t>
+          <t>656937</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>564317</t>
+          <t>564972</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>588048</t>
+          <t>587438</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1205776</t>
+          <t>1204681</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1239770</t>
+          <t>1239532</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,54%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37758</t>
+          <t>39108</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65915</t>
+          <t>66170</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38407</t>
+          <t>38975</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66145</t>
+          <t>68148</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>83932</t>
+          <t>84284</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>123733</t>
+          <t>122074</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>615948</t>
+          <t>615693</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>644105</t>
+          <t>642755</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>644705</t>
+          <t>642702</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>672443</t>
+          <t>671875</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1268979</t>
+          <t>1270638</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1308780</t>
+          <t>1308428</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,95%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38386</t>
+          <t>39579</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69501</t>
+          <t>68795</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,82 +4756,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>6,45%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11,21%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>44244</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>30974</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>59372</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>7,19%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>5,04%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>9,65%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>95924</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>76919</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>120566</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>7,81%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>6,26%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11,33%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>44244</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>31460</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>60800</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>7,19%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>5,11%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>9,88%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>95924</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>77834</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>119328</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>7,81%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>6,33%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>544086</t>
+          <t>544792</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>575201</t>
+          <t>574008</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,82 +4869,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>93,55%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>570884</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>555756</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>584154</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>92,81%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>90,35%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>94,96%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1132791</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1108149</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1151796</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>92,19%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>90,19%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>93,74%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>501</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>570884</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>554328</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>583668</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>92,81%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>90,12%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>94,89%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1003</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1132791</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1109387</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1150881</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>92,19%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>90,29%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>93,67%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>66808</t>
+          <t>68205</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>99728</t>
+          <t>101053</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>68993</t>
+          <t>68172</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>102279</t>
+          <t>103088</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>143868</t>
+          <t>146714</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>193922</t>
+          <t>193989</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,14%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>328687</t>
+          <t>327362</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>361607</t>
+          <t>360210</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>345521</t>
+          <t>344712</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>378807</t>
+          <t>379628</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>682293</t>
+          <t>682226</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>732347</t>
+          <t>729501</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,26%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>160889</t>
+          <t>158129</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>196496</t>
+          <t>195124</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>150046</t>
+          <t>151035</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>188285</t>
+          <t>186923</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>321368</t>
+          <t>321618</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>373699</t>
+          <t>373707</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>113290</t>
+          <t>114662</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>148897</t>
+          <t>151657</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>165711</t>
+          <t>167073</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>203950</t>
+          <t>202961</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>290083</t>
+          <t>290075</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>342414</t>
+          <t>342164</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>51,55%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>155178</t>
+          <t>155785</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>185466</t>
+          <t>184464</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>231186</t>
+          <t>230923</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>270586</t>
+          <t>270120</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>397655</t>
+          <t>398258</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>447487</t>
+          <t>446970</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>70,08%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>63358</t>
+          <t>64360</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>93646</t>
+          <t>93039</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>118393</t>
+          <t>118859</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>157793</t>
+          <t>158056</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>190316</t>
+          <t>190833</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>240148</t>
+          <t>239545</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>37,56%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>559635</t>
+          <t>561934</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>654722</t>
+          <t>651223</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>602855</t>
+          <t>603682</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>697599</t>
+          <t>697331</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1188426</t>
+          <t>1180465</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1318334</t>
+          <t>1318056</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2767033</t>
+          <t>2770532</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2862120</t>
+          <t>2859821</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2859639</t>
+          <t>2859907</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2954383</t>
+          <t>2953556</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5660659</t>
+          <t>5660937</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5790567</t>
+          <t>5798528</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>83,09%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han vacunado de la gripe en la última campaña en 2016</t>
+          <t>Población según si se han vacunado de la gripe en la última campaña en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14061</t>
+          <t>13658</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34500</t>
+          <t>31837</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>9168</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23687</t>
+          <t>25098</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25678</t>
+          <t>26371</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49481</t>
+          <t>51279</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>384963</t>
+          <t>387626</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>405402</t>
+          <t>405805</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>372068</t>
+          <t>370657</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>387091</t>
+          <t>386587</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>765737</t>
+          <t>763939</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>789540</t>
+          <t>788847</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,77%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>15385</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35532</t>
+          <t>35717</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15866</t>
+          <t>16032</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34890</t>
+          <t>34986</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36327</t>
+          <t>36235</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63444</t>
+          <t>63451</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,7 +7119,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>554964</t>
+          <t>554779</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>574643</t>
+          <t>575111</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>528654</t>
+          <t>528558</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>547678</t>
+          <t>547512</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1090596</t>
+          <t>1090589</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1117713</t>
+          <t>1117805</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,86%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10755</t>
+          <t>11020</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28546</t>
+          <t>27924</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30947</t>
+          <t>31381</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57928</t>
+          <t>55991</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46829</t>
+          <t>46018</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77234</t>
+          <t>76768</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>640551</t>
+          <t>641173</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>658342</t>
+          <t>658077</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>603458</t>
+          <t>605395</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>630439</t>
+          <t>630005</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1253249</t>
+          <t>1253715</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1283654</t>
+          <t>1284465</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37697</t>
+          <t>37835</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69294</t>
+          <t>66789</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33097</t>
+          <t>34637</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59958</t>
+          <t>61152</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>78403</t>
+          <t>79454</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118184</t>
+          <t>118326</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>576754</t>
+          <t>579259</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>608351</t>
+          <t>608213</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>589119</t>
+          <t>587925</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>615980</t>
+          <t>614440</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1176941</t>
+          <t>1176799</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1216722</t>
+          <t>1215671</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,87%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>74397</t>
+          <t>73082</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>111201</t>
+          <t>109371</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,82 +8078,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>15,29%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>22,88%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>84698</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>66833</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>105428</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>17,05%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>13,45%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>21,22%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>175453</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>151785</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>202965</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>18,0%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>15,57%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>23,27%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>84698</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>67384</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>101575</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>17,05%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>13,56%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>20,44%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>175453</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>151304</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>201203</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>18,0%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>15,52%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>366717</t>
+          <t>368547</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>403521</t>
+          <t>404836</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,82 +8191,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>84,71%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>412151</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>391421</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>430016</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>82,95%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>78,78%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>86,55%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>703</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>799314</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>771802</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>822982</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>82,0%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>79,18%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>84,43%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>359</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>412151</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>395274</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>429465</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>82,95%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>79,56%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>86,44%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>703</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>799314</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>773564</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>823463</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>82,0%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>79,36%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>84,48%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>138450</t>
+          <t>137304</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>175257</t>
+          <t>173886</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>144592</t>
+          <t>141188</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>185319</t>
+          <t>180066</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>291760</t>
+          <t>293621</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>347571</t>
+          <t>346041</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>48,6%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>159073</t>
+          <t>160444</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>195880</t>
+          <t>197026</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>192443</t>
+          <t>197696</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>233170</t>
+          <t>236574</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>364521</t>
+          <t>366051</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>420332</t>
+          <t>418471</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>58,77%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>158636</t>
+          <t>158686</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>184966</t>
+          <t>183540</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>218366</t>
+          <t>217360</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>259104</t>
+          <t>260898</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>384336</t>
+          <t>385375</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>438311</t>
+          <t>438954</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,79%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>72032</t>
+          <t>73458</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>98362</t>
+          <t>98312</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>141065</t>
+          <t>139271</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>181803</t>
+          <t>182809</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>218856</t>
+          <t>218213</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>272831</t>
+          <t>271792</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,36%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>493254</t>
+          <t>496907</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>581097</t>
+          <t>576882</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>564712</t>
+          <t>568059</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>659929</t>
+          <t>664023</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1079768</t>
+          <t>1085633</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1209766</t>
+          <t>1210414</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,44%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2813253</t>
+          <t>2817468</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2901096</t>
+          <t>2897443</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2884613</t>
+          <t>2880519</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2979830</t>
+          <t>2976483</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5729126</t>
+          <t>5728478</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5859124</t>
+          <t>5853259</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,35%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han vacunado de la gripe en la última campaña en 2023</t>
+          <t>Población según si se han vacunado de la gripe en la última campaña en 2023 (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5438</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34262</t>
+          <t>34276</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25509</t>
+          <t>26028</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57325</t>
+          <t>57953</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38387</t>
+          <t>36195</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>82756</t>
+          <t>78814</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>365725</t>
+          <t>365711</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>394549</t>
+          <t>394841</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>255875</t>
+          <t>255247</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>287691</t>
+          <t>287172</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>630431</t>
+          <t>634373</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>674800</t>
+          <t>676992</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,92%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32974</t>
+          <t>32843</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66023</t>
+          <t>67554</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43907</t>
+          <t>46361</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>95426</t>
+          <t>96312</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>90847</t>
+          <t>91743</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>150611</t>
+          <t>151910</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>357524</t>
+          <t>355993</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>390573</t>
+          <t>390704</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>416078</t>
+          <t>415192</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>467597</t>
+          <t>465143</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>784440</t>
+          <t>783141</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>844204</t>
+          <t>843308</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,19%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68778</t>
+          <t>68841</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>104086</t>
+          <t>102873</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75226</t>
+          <t>74600</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>103520</t>
+          <t>103378</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>150617</t>
+          <t>150690</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>196624</t>
+          <t>195116</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>432252</t>
+          <t>433465</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>467560</t>
+          <t>467497</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>438948</t>
+          <t>439090</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>467242</t>
+          <t>467868</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>882182</t>
+          <t>883690</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>928189</t>
+          <t>928116</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,03%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>58440</t>
+          <t>57474</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>189629</t>
+          <t>192847</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>128171</t>
+          <t>129025</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>173263</t>
+          <t>173386</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>161953</t>
+          <t>173490</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>349465</t>
+          <t>352777</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>698157</t>
+          <t>694939</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>829346</t>
+          <t>830312</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>539235</t>
+          <t>539112</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>584327</t>
+          <t>583473</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1250820</t>
+          <t>1247508</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1438332</t>
+          <t>1426795</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,16%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>184701</t>
+          <t>185336</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>230091</t>
+          <t>228572</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>186522</t>
+          <t>186470</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>220551</t>
+          <t>220480</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>381336</t>
+          <t>381996</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>435909</t>
+          <t>432383</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,07%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>331143</t>
+          <t>332662</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>376533</t>
+          <t>375898</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>325015</t>
+          <t>325086</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>359044</t>
+          <t>359096</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>670890</t>
+          <t>674416</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>725463</t>
+          <t>724803</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,49%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>255409</t>
+          <t>253496</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>282244</t>
+          <t>281510</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>438677</t>
+          <t>439235</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>564187</t>
+          <t>558263</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>707425</t>
+          <t>708131</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>863323</t>
+          <t>869278</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>89,02%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>85921</t>
+          <t>86655</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>112756</t>
+          <t>114669</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>44181</t>
+          <t>50105</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>169691</t>
+          <t>169133</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>113210</t>
+          <t>107255</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>269108</t>
+          <t>268402</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,49%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>239821</t>
+          <t>240525</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>257196</t>
+          <t>257544</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>358834</t>
+          <t>358708</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>379041</t>
+          <t>378724</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>604973</t>
+          <t>605628</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>630468</t>
+          <t>632256</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,23%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>25563</t>
+          <t>25215</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>42938</t>
+          <t>42234</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>46790</t>
+          <t>47107</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>66997</t>
+          <t>67123</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>78122</t>
+          <t>76334</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>103617</t>
+          <t>102962</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>772581</t>
+          <t>761251</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1102113</t>
+          <t>1094074</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1277459</t>
+          <t>1272239</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1863471</t>
+          <t>1826627</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2191821</t>
+          <t>2207379</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2871650</t>
+          <t>2865676</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,25%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2357704</t>
+          <t>2365743</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2687236</t>
+          <t>2698566</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1795964</t>
+          <t>1832808</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2381976</t>
+          <t>2387196</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4247602</t>
+          <t>4253576</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4927431</t>
+          <t>4911873</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>68,99%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P37-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P37-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10219</t>
+          <t>10603</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28454</t>
+          <t>26728</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,82 +748,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,42%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>11439</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5956</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>20801</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>4,46%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>29236</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>19907</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>41769</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>3,05%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>2,07%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,77%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>11439</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>5569</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>19443</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>29236</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>19771</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>43360</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>464760</t>
+          <t>466486</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>482995</t>
+          <t>482611</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,82 +861,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>97,85%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>477</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>455134</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>445772</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>460617</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>97,55%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,54%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>98,72%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>958</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>930551</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>918018</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>939880</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>96,95%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>95,65%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>97,93%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>477</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>455134</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>447130</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>461004</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,55%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>95,83%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>98,81%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>958</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>930551</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>916427</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>940016</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>96,95%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>95,48%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23271</t>
+          <t>23459</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46433</t>
+          <t>47599</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15164</t>
+          <t>14630</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35548</t>
+          <t>34868</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42534</t>
+          <t>42647</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71901</t>
+          <t>74501</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>689056</t>
+          <t>687890</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>712218</t>
+          <t>712030</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>589946</t>
+          <t>590626</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>610330</t>
+          <t>610864</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1289081</t>
+          <t>1286481</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1318448</t>
+          <t>1318335</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23797</t>
+          <t>25157</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48904</t>
+          <t>48600</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31904</t>
+          <t>33096</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58314</t>
+          <t>59313</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61555</t>
+          <t>62687</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96705</t>
+          <t>99714</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>589764</t>
+          <t>590068</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>614871</t>
+          <t>613511</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>630449</t>
+          <t>629450</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>656859</t>
+          <t>655667</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1230726</t>
+          <t>1227717</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1265876</t>
+          <t>1264744</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,28%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27069</t>
+          <t>27218</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52360</t>
+          <t>52977</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16930</t>
+          <t>17860</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36617</t>
+          <t>37973</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49451</t>
+          <t>51941</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82394</t>
+          <t>81826</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>466787</t>
+          <t>466170</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>492078</t>
+          <t>491929</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>479025</t>
+          <t>477669</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>498712</t>
+          <t>497782</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>952395</t>
+          <t>952963</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>985338</t>
+          <t>982848</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>94,98%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57791</t>
+          <t>57409</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86268</t>
+          <t>88433</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57085</t>
+          <t>57008</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>88087</t>
+          <t>88522</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>122776</t>
+          <t>119498</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>163212</t>
+          <t>163747</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,71%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>300442</t>
+          <t>298277</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>328919</t>
+          <t>329301</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>315899</t>
+          <t>315464</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>346901</t>
+          <t>346978</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>627484</t>
+          <t>626949</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>667920</t>
+          <t>671198</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,89%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>98930</t>
+          <t>100433</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>132815</t>
+          <t>132348</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>133731</t>
+          <t>134573</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>168815</t>
+          <t>169419</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>244513</t>
+          <t>244028</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>291984</t>
+          <t>291680</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>45,96%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>158854</t>
+          <t>159321</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>192739</t>
+          <t>191236</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>174119</t>
+          <t>173515</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>209203</t>
+          <t>208361</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>342619</t>
+          <t>342923</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>390090</t>
+          <t>390575</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,55%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>129604</t>
+          <t>128141</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>155416</t>
+          <t>155103</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>186620</t>
+          <t>186968</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>223557</t>
+          <t>225056</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>325851</t>
+          <t>322914</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>370871</t>
+          <t>370048</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>68,05%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>54467</t>
+          <t>54780</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>80279</t>
+          <t>81742</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>110351</t>
+          <t>108852</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>147288</t>
+          <t>146940</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>172920</t>
+          <t>173743</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>217940</t>
+          <t>220877</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,62%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>417913</t>
+          <t>416507</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>490096</t>
+          <t>494851</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>494083</t>
+          <t>490061</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>574991</t>
+          <t>578056</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>933527</t>
+          <t>932541</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1045896</t>
+          <t>1048028</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2784683</t>
+          <t>2779928</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2856866</t>
+          <t>2858272</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2802309</t>
+          <t>2799244</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2883217</t>
+          <t>2887239</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5606183</t>
+          <t>5604051</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5718552</t>
+          <t>5719538</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,98%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17760</t>
+          <t>18162</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39674</t>
+          <t>40518</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>8090</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23272</t>
+          <t>24279</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31001</t>
+          <t>28641</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57740</t>
+          <t>55822</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>412520</t>
+          <t>411676</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>434434</t>
+          <t>434032</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>406958</t>
+          <t>405951</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>422330</t>
+          <t>422140</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>824684</t>
+          <t>826602</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>851423</t>
+          <t>853783</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,75%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30150</t>
+          <t>30468</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56153</t>
+          <t>55462</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22817</t>
+          <t>22719</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45283</t>
+          <t>44629</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>57810</t>
+          <t>58412</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>92661</t>
+          <t>91175</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>630934</t>
+          <t>631625</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>656937</t>
+          <t>656619</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>564972</t>
+          <t>565626</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>587438</t>
+          <t>587536</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1204681</t>
+          <t>1206167</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1239532</t>
+          <t>1238930</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,5%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39108</t>
+          <t>38202</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66170</t>
+          <t>66879</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38975</t>
+          <t>38825</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68148</t>
+          <t>65944</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>84284</t>
+          <t>82657</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>122074</t>
+          <t>123857</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>615693</t>
+          <t>614984</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>642755</t>
+          <t>643661</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>642702</t>
+          <t>644906</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>671875</t>
+          <t>672025</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1270638</t>
+          <t>1268855</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1308428</t>
+          <t>1310055</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,07%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39579</t>
+          <t>38376</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68795</t>
+          <t>68286</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30974</t>
+          <t>32578</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59372</t>
+          <t>60736</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>76919</t>
+          <t>77373</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>120566</t>
+          <t>118741</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>544792</t>
+          <t>545301</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>574008</t>
+          <t>575211</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>555756</t>
+          <t>554392</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>584154</t>
+          <t>582550</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1108149</t>
+          <t>1109974</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1151796</t>
+          <t>1151342</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,7%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>68205</t>
+          <t>67245</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>101053</t>
+          <t>101410</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>68172</t>
+          <t>70546</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>103088</t>
+          <t>104611</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>146714</t>
+          <t>146239</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>193989</t>
+          <t>193936</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>327362</t>
+          <t>327005</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>360210</t>
+          <t>361170</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>344712</t>
+          <t>343189</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>379628</t>
+          <t>377254</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>682226</t>
+          <t>682279</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>729501</t>
+          <t>729976</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,31%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>158129</t>
+          <t>160497</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>195124</t>
+          <t>197425</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>151035</t>
+          <t>150325</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>186923</t>
+          <t>187437</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>321618</t>
+          <t>321351</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>373707</t>
+          <t>374707</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>56,45%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>114662</t>
+          <t>112361</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>151657</t>
+          <t>149289</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>167073</t>
+          <t>166559</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>202961</t>
+          <t>203671</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>290075</t>
+          <t>289075</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>342164</t>
+          <t>342431</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,59%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>155785</t>
+          <t>154658</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>184464</t>
+          <t>187621</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>230923</t>
+          <t>231103</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>270120</t>
+          <t>270027</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>398258</t>
+          <t>398339</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>446970</t>
+          <t>448978</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>70,39%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>64360</t>
+          <t>61203</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>93039</t>
+          <t>94166</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>118859</t>
+          <t>118952</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>158056</t>
+          <t>157876</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>190833</t>
+          <t>188825</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>239545</t>
+          <t>239464</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,55%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>561934</t>
+          <t>559303</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>651223</t>
+          <t>651651</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>603682</t>
+          <t>601675</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>697331</t>
+          <t>696575</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1180465</t>
+          <t>1188590</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1318056</t>
+          <t>1322663</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,95%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2770532</t>
+          <t>2770104</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2859821</t>
+          <t>2862452</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2859907</t>
+          <t>2860663</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2953556</t>
+          <t>2955563</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5660937</t>
+          <t>5656330</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5798528</t>
+          <t>5790403</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>82,97%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13658</t>
+          <t>13708</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31837</t>
+          <t>32621</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9168</t>
+          <t>8617</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25098</t>
+          <t>23506</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26371</t>
+          <t>25856</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51279</t>
+          <t>50289</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>387626</t>
+          <t>386842</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>405805</t>
+          <t>405755</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>370657</t>
+          <t>372249</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>386587</t>
+          <t>387138</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>763939</t>
+          <t>764929</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>788847</t>
+          <t>789362</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15385</t>
+          <t>15111</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35717</t>
+          <t>36072</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16032</t>
+          <t>15477</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34986</t>
+          <t>33745</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36235</t>
+          <t>35343</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63451</t>
+          <t>61607</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>554779</t>
+          <t>554424</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>575111</t>
+          <t>575385</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>528558</t>
+          <t>529799</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>547512</t>
+          <t>548067</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1090589</t>
+          <t>1092433</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1117805</t>
+          <t>1118697</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11020</t>
+          <t>10298</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27924</t>
+          <t>29111</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31381</t>
+          <t>31464</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55991</t>
+          <t>58040</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46018</t>
+          <t>45415</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>76768</t>
+          <t>76780</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,7 +7462,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>641173</t>
+          <t>639986</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>658077</t>
+          <t>658799</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>605395</t>
+          <t>603346</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>630005</t>
+          <t>629922</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1253715</t>
+          <t>1253703</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1284465</t>
+          <t>1285068</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7580,7 +7580,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,59%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37835</t>
+          <t>38433</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66789</t>
+          <t>67518</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34637</t>
+          <t>33986</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61152</t>
+          <t>60204</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>79454</t>
+          <t>76684</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118326</t>
+          <t>116380</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>579259</t>
+          <t>578530</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>608213</t>
+          <t>607615</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>587925</t>
+          <t>588873</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>614440</t>
+          <t>615091</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1176799</t>
+          <t>1178745</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1215671</t>
+          <t>1218441</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,08%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>73082</t>
+          <t>75048</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>109371</t>
+          <t>110528</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>66833</t>
+          <t>67186</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>105428</t>
+          <t>103192</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>151785</t>
+          <t>149957</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>202965</t>
+          <t>202101</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>368547</t>
+          <t>367390</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>404836</t>
+          <t>402870</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>391421</t>
+          <t>393657</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>430016</t>
+          <t>429663</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>771802</t>
+          <t>772666</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>822982</t>
+          <t>824810</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,62%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>137304</t>
+          <t>139374</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>173886</t>
+          <t>177114</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>141188</t>
+          <t>142474</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>180066</t>
+          <t>182530</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>293621</t>
+          <t>293018</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>346041</t>
+          <t>345352</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,5%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>160444</t>
+          <t>157216</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>197026</t>
+          <t>194956</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>197696</t>
+          <t>195232</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>236574</t>
+          <t>235288</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>366051</t>
+          <t>366740</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>418471</t>
+          <t>419074</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,85%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>158686</t>
+          <t>157508</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>183540</t>
+          <t>185980</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>217360</t>
+          <t>216929</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>260898</t>
+          <t>261279</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>385375</t>
+          <t>387414</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>438954</t>
+          <t>438425</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>66,71%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>73458</t>
+          <t>71018</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>98312</t>
+          <t>99490</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>139271</t>
+          <t>138890</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>182809</t>
+          <t>183240</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>218213</t>
+          <t>218742</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>271792</t>
+          <t>269753</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,05%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>496907</t>
+          <t>492829</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>576882</t>
+          <t>574832</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>568059</t>
+          <t>564882</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>664023</t>
+          <t>667564</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1085633</t>
+          <t>1088262</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1210414</t>
+          <t>1210238</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2817468</t>
+          <t>2819518</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2897443</t>
+          <t>2901521</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2880519</t>
+          <t>2876978</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2976483</t>
+          <t>2979660</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5728478</t>
+          <t>5728654</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5853259</t>
+          <t>5850630</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,32%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>15106</t>
+          <t>13721</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5146</t>
+          <t>5535</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34276</t>
+          <t>28784</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>39347</t>
+          <t>43519</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26028</t>
+          <t>29676</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57953</t>
+          <t>63138</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>54452</t>
+          <t>57240</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36195</t>
+          <t>38700</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>78814</t>
+          <t>82527</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>384881</t>
+          <t>394072</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>365711</t>
+          <t>379009</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>394841</t>
+          <t>402258</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>273853</t>
+          <t>318993</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>255247</t>
+          <t>299374</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>287172</t>
+          <t>332836</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>658735</t>
+          <t>713065</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>634373</t>
+          <t>687778</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>676992</t>
+          <t>731605</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,98%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>47019</t>
+          <t>53102</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32843</t>
+          <t>38285</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67554</t>
+          <t>72888</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>74303</t>
+          <t>81360</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46361</t>
+          <t>64148</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>96312</t>
+          <t>99708</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>121322</t>
+          <t>134462</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>91743</t>
+          <t>110297</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>151910</t>
+          <t>164035</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>376528</t>
+          <t>423788</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>355993</t>
+          <t>404002</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>390704</t>
+          <t>438605</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>437201</t>
+          <t>419723</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>415192</t>
+          <t>401375</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>465143</t>
+          <t>436935</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>813729</t>
+          <t>843511</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>783141</t>
+          <t>813938</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>843308</t>
+          <t>867676</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>88,72%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>84718</t>
+          <t>92585</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68841</t>
+          <t>75174</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>102873</t>
+          <t>112715</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>88334</t>
+          <t>98500</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>74600</t>
+          <t>83225</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>103378</t>
+          <t>115831</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>173052</t>
+          <t>191085</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>150690</t>
+          <t>166500</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>195116</t>
+          <t>217049</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,46%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>451620</t>
+          <t>528252</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>433465</t>
+          <t>508122</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>467497</t>
+          <t>545663</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>454134</t>
+          <t>523639</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>439090</t>
+          <t>506308</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>467868</t>
+          <t>538914</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>905754</t>
+          <t>1051891</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>883690</t>
+          <t>1025927</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>928116</t>
+          <t>1076476</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,6%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>131581</t>
+          <t>143148</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57474</t>
+          <t>122239</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>192847</t>
+          <t>165071</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>154476</t>
+          <t>166690</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>129025</t>
+          <t>148558</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>173386</t>
+          <t>184305</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>286057</t>
+          <t>309838</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>173490</t>
+          <t>282732</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>352777</t>
+          <t>339780</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>23,64%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>756205</t>
+          <t>557469</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>694939</t>
+          <t>535546</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>830312</t>
+          <t>578378</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>558022</t>
+          <t>569805</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>539112</t>
+          <t>552190</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>583473</t>
+          <t>587937</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1314228</t>
+          <t>1127274</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1247508</t>
+          <t>1097332</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1426795</t>
+          <t>1154380</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>80,33%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>206427</t>
+          <t>222872</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>185336</t>
+          <t>201251</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>228572</t>
+          <t>245314</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>202107</t>
+          <t>226887</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>186470</t>
+          <t>209335</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>220480</t>
+          <t>244851</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>408533</t>
+          <t>449759</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>381996</t>
+          <t>419251</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>432383</t>
+          <t>479313</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>39,37%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>354807</t>
+          <t>386474</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>332662</t>
+          <t>364032</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>375898</t>
+          <t>408095</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,42%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>343459</t>
+          <t>381246</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>325086</t>
+          <t>363282</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>359096</t>
+          <t>398798</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>698266</t>
+          <t>767720</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>674416</t>
+          <t>738166</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>724803</t>
+          <t>798228</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>65,56%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>545566</t>
+          <t>608133</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>545566</t>
+          <t>608133</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>545566</t>
+          <t>608133</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1106799</t>
+          <t>1217479</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1106799</t>
+          <t>1217479</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1106799</t>
+          <t>1217479</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>269319</t>
+          <t>293850</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>253496</t>
+          <t>278223</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>281510</t>
+          <t>307951</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>500941</t>
+          <t>324215</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>439235</t>
+          <t>311515</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>558263</t>
+          <t>337134</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>770260</t>
+          <t>618065</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>708131</t>
+          <t>597411</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>869278</t>
+          <t>639320</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>75,55%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>98846</t>
+          <t>113230</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>86655</t>
+          <t>99129</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>114669</t>
+          <t>128857</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>107427</t>
+          <t>114951</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>50105</t>
+          <t>102032</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>169133</t>
+          <t>127651</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>206273</t>
+          <t>228181</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>107255</t>
+          <t>206926</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>268402</t>
+          <t>248835</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>29,4%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>249273</t>
+          <t>273157</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>240525</t>
+          <t>262359</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>257544</t>
+          <t>282830</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>369069</t>
+          <t>402882</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>358708</t>
+          <t>391473</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>378724</t>
+          <t>412809</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>618342</t>
+          <t>676039</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>605628</t>
+          <t>660631</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>632256</t>
+          <t>689660</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,01%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>33486</t>
+          <t>37041</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>25215</t>
+          <t>27368</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>42234</t>
+          <t>47839</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>56762</t>
+          <t>61727</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>47107</t>
+          <t>51800</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>67123</t>
+          <t>73136</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>90248</t>
+          <t>98768</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>76334</t>
+          <t>85147</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>102962</t>
+          <t>114176</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1003443</t>
+          <t>1092435</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>761251</t>
+          <t>1038257</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1094074</t>
+          <t>1148687</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1428576</t>
+          <t>1344053</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1272239</t>
+          <t>1296631</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1826627</t>
+          <t>1403302</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2432019</t>
+          <t>2436488</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2207379</t>
+          <t>2365011</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2865676</t>
+          <t>2513361</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>34,59%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2456374</t>
+          <t>2440327</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2365743</t>
+          <t>2384075</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2698566</t>
+          <t>2494505</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2230859</t>
+          <t>2390084</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1832808</t>
+          <t>2330835</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2387196</t>
+          <t>2437506</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>4687233</t>
+          <t>4830411</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4253576</t>
+          <t>4753538</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4911873</t>
+          <t>4901888</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>67,46%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3659435</t>
+          <t>3734137</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3659435</t>
+          <t>3734137</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3659435</t>
+          <t>3734137</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7119252</t>
+          <t>7266899</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7119252</t>
+          <t>7266899</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7119252</t>
+          <t>7266899</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
